--- a/experiments/rq1-3-4-5/methods/visidroid_no_vision/all_tasks.xlsx
+++ b/experiments/rq1-3-4-5/methods/visidroid_no_vision/all_tasks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minhh\OneDrive\Documents\mobile-testing\methods\visidroid_no_vision\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\visidroid\visidroid\experiments\rq1-3-4-5\methods\visidroid_no_vision\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4861E8E7-0234-487C-91B9-5C249235DAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F058A91E-98DF-4960-B168-AB66A9FAE39E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="758">
   <si>
     <t>app_name</t>
   </si>
@@ -49,12 +49,21 @@
     <t>Calendar</t>
   </si>
   <si>
+    <t>calendar</t>
+  </si>
+  <si>
+    <t>camera</t>
+  </si>
+  <si>
     <t>Camera</t>
   </si>
   <si>
     <t>clock</t>
   </si>
   <si>
+    <t>contacts</t>
+  </si>
+  <si>
     <t>dialer</t>
   </si>
   <si>
@@ -64,9 +73,18 @@
     <t>gallery</t>
   </si>
   <si>
+    <t>messenger</t>
+  </si>
+  <si>
     <t>musicplayer</t>
   </si>
   <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>voicerecorder</t>
+  </si>
+  <si>
     <t>Add all my contacts' birthdays into the calendar</t>
   </si>
   <si>
@@ -461,6 +479,42 @@
   </si>
   <si>
     <t>Use player to play 'test2.m4a'</t>
+  </si>
+  <si>
+    <t>Add the event of 'VisitParents' on july 30, remind me 1 hour before, save it</t>
+  </si>
+  <si>
+    <t>Add the holidays of South Africa to the calendar and list all the events in 2023</t>
+  </si>
+  <si>
+    <t>Create a new group 'Classmates',add Alice,Bob and Jack to the new group, and text to the group 'GatheringInTheOldPlace'</t>
+  </si>
+  <si>
+    <t>Open dialpad and call 911</t>
+  </si>
+  <si>
+    <t>Search call history with Bob</t>
+  </si>
+  <si>
+    <t>Switch custom colors to light and save it</t>
+  </si>
+  <si>
+    <t>Change the storage type to sd card</t>
+  </si>
+  <si>
+    <t>Temporarily show hidden files</t>
+  </si>
+  <si>
+    <t>Do not display GIF images in the Gallery app</t>
+  </si>
+  <si>
+    <t>Change the name of the chat with Alice to 'team_discussion'</t>
+  </si>
+  <si>
+    <t>Create a text note called 'test', type '12345678', and search for '234'</t>
+  </si>
+  <si>
+    <t>Export note 'Diary' as file diary.txt, only export the current file content</t>
   </si>
   <si>
     <t>Jade Green attempted to add all contact birthdays to the calendar, but the app indicated that no birthdays were found in the contacts.</t>
@@ -882,14 +936,15 @@
 - ACTION 3: touched on a button that has text "OK"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "New Event"
-- ACTION 2: touched on a button that has content-desc "New Event"
-- ACTION 3: filled a focused textfield that has text "Title" with the text "John Doe's Anniversary"
-- ACTION 4: touched on a button that has text "October 25 (Fri)"
-- ACTION 5: touched on a button that has text "OK"
-- ACTION 6: touched on a button that has text "No repetition"
-- ACTION 7: touched on a button that has text "Yearly"
-- ACTION 8: touched on a button that has content-desc "Save"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "New Event"
+- ACTION 2: Jade Green touched on a button that has text "Event"
+- ACTION 3: Jade Green filled a focused textfield that has text "Title" with the text "[Contact's Name] Anniversary"
+- ACTION 4: Jade Green touched on a button that has text "February 24 (Mon)"
+- ACTION 5: Jade Green touched on a button that has text "OK"
+- ACTION 6: Jade Green touched on a button that has text "No repetition"
+- ACTION 7: Jade Green touched on a button that has text "Yearly"
+- ACTION 8: Jade Green touched on a button that has content_desc "Save"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "New Event"
@@ -921,11 +976,17 @@
 - ACTION 4: touched on a button that has text "OK"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Settings"
-- ACTION 3: touched on a button that has text "Customize notifications"
-- ACTION 4: touched on a button that has text "deadlines, ~2 notifications per week"
-- ACTION 5: touched on a button that has text "Advanced, Sound, Vibration, Override Do Not Disturb"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Settings"
+- ACTION 3: Jade Green touched on a button that has text "Customize notifications"
+- ACTION 4: Jade Green touched on a button that has text "Advanced, Allow notification dot"
+- ACTION 5: Jade Green touched on a button that has text "Calendar"
+- ACTION 6: Jade Green touched on a button that has content_desc "Back"
+- ACTION 7: Jade Green touched on a button that has text "Customize notifications"
+- ACTION 8: Jade Green touched on a button that has text "Advanced, Allow notification dot"
+- ACTION 9: Jade Green touched on a button that has content_desc "Back"
+- ACTION 10: Jade Green touched on a button that has text "Customize notifications"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "More options"
@@ -936,47 +997,44 @@
 - ACTION 6: touched on a button that has text "OK"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Search"
-- ACTION 2: filled a focused textfield that has text "Search" with the text "snooze time"
-- ACTION 3: touched on a button that has content-desc "More options"
-- ACTION 4: touched on a button that has text "Settings"
-- ACTION 5: touched on a button that has text "Customize notifications"
-- ACTION 6: touched on a button that has content-desc "Search settings"
-- ACTION 7: touched on a button that has content-desc "Navigate up"
-- ACTION 8: touched on a button that has content-desc "Back"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Settings"
+- ACTION 3: Jade Green scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, Customize widget colors[...and more]"
+- ACTION 4: Jade Green touched on a button that has text "Snooze time, 10 minutes"
+- ACTION 5: Jade Green touched on a button that has text "30 minutes"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Change view"
 - ACTION 2: touched on a button that has text "Yearly view"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "New Event"
-- ACTION 2: touched on a button that has content-desc "New Event"
-- ACTION 3: filled a focused textfield that has text "Title" with the text "laundry"
-- ACTION 4: touched on a button that has content-desc "Save"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/small_month_view"
-- ACTION 2: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"
-- ACTION 3: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"
-- ACTION 4: touched on a button that has content-desc "More options"
-- ACTION 5: touched on a button that has content-desc "More options"
-- ACTION 6: touched on a button that has content-desc "Change view"
-- ACTION 7: touched on a button that has text "Monthly view"
-- ACTION 8: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"
-- ACTION 9: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Settings"
-- ACTION 3: touched on a button that has text "Manage event types"
-- ACTION 4: touched on a button that has content-desc "Back"
-- ACTION 5: touched on a button that has content-desc "Back"
-- ACTION 6: touched on a button that has content-desc "More options"
-- ACTION 7: touched on a button that has content-desc "Filter events by type"
-- ACTION 8: touched on a button that has text "Cancel"
-- ACTION 9: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/small_month_view"
-- ACTION 10: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "New Event"
+- ACTION 2: Jade Green filled a focused textfield that has text "Title" with the text "laundry"
+- ACTION 3: Jade Green touched on a button that has content_desc "Save"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "New Event"
+- ACTION 2: Jade Green filled a focused textfield that has text "Title" with the text "homework"
+- ACTION 3: Jade Green touched on a button that has text "No repetition"
+- ACTION 4: Jade Green touched on a button that has text "Daily"
+- ACTION 5: Jade Green touched on a button that has content_desc "Save"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Settings"
+- ACTION 3: Jade Green touched on a button that has text "Manage event types"
+- ACTION 4: Jade Green touched on a button that has content_desc "Back"
+- ACTION 5: Jade Green pressed "BACK" button to navigate back
+- ACTION 6: Jade Green touched on a button that has content_desc "More options"
+- ACTION 7: Jade Green pressed "BACK" button to navigate back
+- ACTION 8: Jade Green touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"
+- ACTION 9: Jade Green touched on a button that has content_desc "Go to today"
+- ACTION 10: Jade Green touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"
+- ACTION 11: Jade Green touched on a button that has content_desc "Delete"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "More options"
@@ -984,15 +1042,18 @@
 - ACTION 3: touched on a button that has text "Start week on, Monday"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Settings"
-- ACTION 3: touched on a button that has content-desc "Back"
-- ACTION 4: touched on a button that has content-desc "More options"
-- ACTION 5: touched on a button that has text "Print"
-- ACTION 6: touched on a button that has content-desc "Save to PDF"
-- ACTION 7: touched on a button that has content-desc "More options"
-- ACTION 8: touched on a button that has text "Settings"
-- ACTION 9: touched on a button that has content-desc "Back"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Print"
+- ACTION 3: Jade Green pressed "BACK" button to navigate back
+- ACTION 4: Jade Green touched on a button that has content_desc "More options"
+- ACTION 5: Jade Green touched on a button that has text "Go to date"
+- ACTION 6: Jade Green touched on a button that has text "Cancel"
+- ACTION 7: Jade Green touched on a button that has content_desc "More options"
+- ACTION 8: Jade Green pressed "BACK" button to navigate back
+- ACTION 9: Jade Green touched on a button that has content_desc "More options"
+- ACTION 10: Jade Green touched on a button that has text "Settings"
+- ACTION 11: Jade Green scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, Customize widget colors[...and more]"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Search"
@@ -1005,18 +1066,16 @@
 - ACTION 4: touched on a checkbox that has text "Use 24-hour time format"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "View last captured media"
-- ACTION 2: touched on a button that has content-desc "View last captured media"
-- ACTION 3: waited for a loading state to finish
-- ACTION 4: touched on a button that has content-desc "View last captured media"
-- ACTION 5: waited for a loading state to finish
-- ACTION 6: touched on a button that has content-desc "View last captured media"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: waited for a loading state to finish
-- ACTION 2: touched on a button that has content-desc "View last captured media"
-- ACTION 3: touched on a button that has content-desc "More options"
-- ACTION 4: touched on a button that has text "Details"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green waited for a loading state to finish
+- ACTION 2: Jade Green touched on a button that has content_desc "View last captured media"
+- ACTION 3: Jade Green touched on a button that has content_desc "More options"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green pressed "BACK" button to navigate back
+- ACTION 2: Jade Green touched on a button that has content_desc "View last captured media"
+- ACTION 3: Jade Green touched on a button that has content_desc "More options"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Settings"
@@ -1024,102 +1083,112 @@
 - ACTION 3: touched on a checked checkbox that has text "Shutter sound"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "View last captured media"
-- ACTION 2: touched on a button that has content-desc "View last captured media"
-- ACTION 3: touched on a button that has content-desc "View last captured media"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "View last captured media"
-- ACTION 2: touched on a button that has content-desc "More options"
-- ACTION 3: touched on a button that has text "Details"
-- ACTION 4: touched on a button that has text "Close"
-- ACTION 5: touched on a button that has content-desc "View last captured media"
-- ACTION 6: touched on a button that has content-desc "More options"
-- ACTION 7: touched on a button that has content-desc "More options"
-- ACTION 8: touched on a button that has content-desc "DCIM, Navigate up"
-- ACTION 9: touched on a button that has content-desc "DCIM, Navigate up"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green waited for a loading state to finish
+- ACTION 2: Jade Green touched on a button that has text "Gallery"
+- ACTION 3: Jade Green touched on a button that has content_desc "View last captured media"
+- ACTION 4: Jade Green touched on a button that has content_desc "More options"
+- ACTION 5: Jade Green touched on a button that has content_desc "DCIM, Navigate up"
+- ACTION 6: Jade Green touched on a button that has content_desc "Share with Print"
+- ACTION 7: Jade Green long touched on a button that has content_desc "More options"
+- ACTION 8: Jade Green pressed "BACK" button to navigate back
+- ACTION 9: Jade Green touched on a button that has content_desc "View last captured media"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green waited for a loading state to finish
+- ACTION 2: Jade Green touched on a button that has content_desc "View last captured media"
+- ACTION 3: Jade Green touched on a button that has resource_id "android:id/expand_activities_button"
+- ACTION 4: Jade Green touched on a button that has content_desc "More options"
+- ACTION 5: Jade Green long touched on a button that has content_desc "More options"
+- ACTION 6: Jade Green pressed "BACK" button to navigate back
+- ACTION 7: Jade Green touched on a button that has content_desc "View last captured media"
+- ACTION 8: Jade Green touched on a button that has content_desc "More options"
+- ACTION 9: Jade Green long touched on a button that has content_desc "More options"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "View last captured media"</t>
   </si>
   <si>
-    <t>- ACTION 1: waited for a loading state to finish
-- ACTION 2: touched on a button that has content-desc "View last captured media"
-- ACTION 3: touched on a button that has resource_id "android:id/expand_activities_button"
-- ACTION 4: touched on a button that has content-desc "More options"
-- ACTION 5: touched on a button that has resource_id "android:id/expand_activities_button"
-- ACTION 6: touched on a button that has text "Print"
-- ACTION 7: touched on a button that has content-desc "View last captured media"
-- ACTION 8: touched on a button that has content-desc "Share with Print"
-- ACTION 9: touched on a button that has content-desc "Share with Print"
-- ACTION 10: touched on a button that has content-desc "Share with Print"
-- ACTION 11: touched on a button that has content-desc "Share with Print"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has text "Video"
-- ACTION 2: touched on a button that has content-desc "Shutter"
-- ACTION 3: touched on a selected button that has content-desc "Shutter"
-- ACTION 4: touched on a button that has content-desc "Shutter"
-- ACTION 5: touched on a selected button that has content-desc "Shutter"
-- ACTION 6: touched on a button that has content-desc "Shutter"
-- ACTION 7: touched on a selected button that has content-desc "Shutter"
-- ACTION 8: touched on a button that has content-desc "Shutter"
-- ACTION 9: waited for a loading state to finish
-- ACTION 10: touched on a selected button that has content-desc "Shutter"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: waited for a loading state to finish
-- ACTION 2: touched on a button that has content-desc "View last captured media"
-- ACTION 3: touched on a button that has content-desc "More options"
-- ACTION 4: long touched on a button that has content-desc "More options"
-- ACTION 5: touched on a button that has content-desc "View last captured media"
-- ACTION 6: touched on a button that has content-desc "More options"
-- ACTION 7: waited for a loading state to finish</t>
-  </si>
-  <si>
-    <t>- ACTION 1: waited for a loading state to finish
-- ACTION 2: touched on a button that has content-desc "View last captured media"
-- ACTION 3: touched on a button that has content-desc "More options"
-- ACTION 4: touched on a button that has content-desc "More options"
-- ACTION 5: touched on a button that has content-desc "More options"
-- ACTION 6: touched on a button that has content-desc "More options"
-- ACTION 7: touched on a button that has content-desc "View last captured media"
-- ACTION 8: touched on a button that has content-desc "More options"
-- ACTION 9: touched on a button that has resource_id "android:id/expand_activities_button"
-- ACTION 10: touched on a button that has resource_id "android:id/expand_activities_button"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: waited for a loading state to finish
-- ACTION 2: touched on a button that has content-desc "View last captured media"
-- ACTION 3: touched on a button that has content-desc "More options"
-- ACTION 4: touched on a button that has content-desc "More options"
-- ACTION 5: touched on a button that has content-desc "More options"
-- ACTION 6: touched on a button that has content-desc "More options"
-- ACTION 7: touched on a button that has content-desc "Share with Print"
-- ACTION 8: Press the back button because you stayed on the pages not belonging to the target app for too long
-- ACTION 9: touched on a button that has content-desc "View last captured media"
-- ACTION 10: touched on a button that has content-desc "More options"
-- ACTION 11: touched on a button that has content-desc "More options"
-- ACTION 12: touched on a button that has content-desc "More options"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Settings"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "View last captured media"
+- ACTION 2: Jade Green touched on a button that has content_desc "Share with Print"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green pressed "BACK" button to navigate back
+- ACTION 2: Jade Green touched on a button that has text "Video"
+- ACTION 3: Jade Green touched on a button that has content_desc "Shutter"
+- ACTION 4: Jade Green touched on a selected button that has content_desc "Shutter"
+- ACTION 5: Jade Green touched on a button that has content_desc "Shutter"
+- ACTION 6: Jade Green touched on a selected button that has content_desc "Shutter"
+- ACTION 7: Jade Green touched on a button that has content_desc "Shutter"
+- ACTION 8: Jade Green touched on a selected button that has content_desc "Shutter"
+- ACTION 9: Jade Green touched on a button that has content_desc "Shutter"
+- ACTION 10: Jade Green waited for a loading state to finish
+- ACTION 11: Jade Green touched on a selected button that has content_desc "Shutter"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "View last captured media"
+- ACTION 2: Jade Green pressed "BACK" button to navigate back
+- ACTION 3: Jade Green touched on a button that has content_desc "View last captured media"
+- ACTION 4: Jade Green pressed "BACK" button to navigate back
+- ACTION 5: Jade Green touched on a button that has content_desc "Settings"
+- ACTION 6: Jade Green touched on a button that has content_desc "Back"
+- ACTION 7: Jade Green touched on a button that has content_desc "View last captured media"
+- ACTION 8: Jade Green pressed "BACK" button to navigate back
+- ACTION 9: Jade Green touched on a button that has content_desc "View last captured media"
+- ACTION 10: Jade Green pressed "BACK" button to navigate back
+- ACTION 11: Jade Green touched on a button that has content_desc "View last captured media"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "View last captured media"
+- ACTION 2: Jade Green touched on a button that has content_desc "More options"
+- ACTION 3: Jade Green touched on a button that has text "Crop"
+- ACTION 4: Jade Green touched on a button that has text "SAVE"
+- ACTION 5: Jade Green pressed "BACK" button to navigate back
+- ACTION 6: Jade Green touched on a button that has content_desc "View last captured media"
+- ACTION 7: Jade Green touched on a button that has content_desc "More options"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green waited for a loading state to finish
+- ACTION 2: Jade Green touched on a button that has content_desc "View last captured media"
+- ACTION 3: Jade Green touched on a button that has content_desc "More options"
+- ACTION 4: Jade Green touched on a button that has content_desc "Share with Print"
+- ACTION 5: Jade Green touched on a button that has content_desc "DCIM, Navigate up"
+- ACTION 6: Jade Green touched on a button that has resource_id "android:id/expand_activities_button"
+- ACTION 7: Jade Green touched on a button that has content_desc "DCIM, Navigate up"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green pressed "BACK" button to navigate back
+- ACTION 2: Jade Green touched on a button that has text "Camera"
+- ACTION 3: Jade Green touched on a button that has content_desc "Settings"
+- ACTION 4: Jade Green touched on a button that has text "Photo compression quality, 80%"
+- ACTION 5: Jade Green touched on a button that has text "50%"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Toggle front/back camera"
 - ACTION 2: touched on a button that has content-desc "Shutter"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has text "Video"
-- ACTION 2: touched on a button that has content-desc "Toggle front/back camera"
-- ACTION 3: touched on a button that has content-desc "Shutter"
-- ACTION 4: touched on a selected button that has content-desc "Shutter"
-- ACTION 5: touched on a button that has content-desc "Shutter"
-- ACTION 6: touched on a selected button that has content-desc "Shutter"
-- ACTION 7: touched on a button that has content-desc "Shutter"
-- ACTION 8: touched on a selected button that has content-desc "Shutter"
-- ACTION 9: touched on a button that has content-desc "Shutter"
-- ACTION 10: touched on a selected button that has content-desc "Shutter"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has text "Video"
+- ACTION 2: Jade Green touched on a button that has content_desc "Toggle front/back camera"
+- ACTION 3: Jade Green touched on a button that has content_desc "Shutter"
+- ACTION 4: Jade Green touched on a selected button that has content_desc "Shutter"
+- ACTION 5: Jade Green touched on a button that has content_desc "Shutter"
+- ACTION 6: Jade Green touched on a selected button that has content_desc "Shutter"
+- ACTION 7: Jade Green touched on a button that has content_desc "Shutter"
+- ACTION 8: Jade Green touched on a selected button that has content_desc "Shutter"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Settings"
+- ACTION 2: Jade Green touched on a checkbox that has text "Use volume buttons as shutter"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "New Timer"
@@ -1151,18 +1220,21 @@
     <t>- ACTION 1: touched on a button that has text "Clock"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Settings"
-- ACTION 2: touched on a button that has text "Always use same snooze time"
-- ACTION 3: touched on a button that has text "Snooze time, 10 minutes"
-- ACTION 4: touched on a button that has text "5 minutes"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Settings"
-- ACTION 2: touched on a button that has content-desc "Back"
-- ACTION 3: touched on a button that has text "Alarm"
-- ACTION 4: touched on a button that has content-desc "Sort by"
-- ACTION 5: touched on a button that has text "Day and Alarm time"
-- ACTION 6: touched on a button that has text "OK"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Settings"
+- ACTION 2: Jade Green touched on a button that has text "Snooze time, 10 minutes"
+- ACTION 3: Jade Green touched on a button that has text "5 minutes"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Settings"
+- ACTION 2: Jade Green scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, Customize widget colors[...and more]"
+- ACTION 3: Jade Green scrolled down on a scrollable area that has text "Customize widget colors, GENERAL, Prevent phone from sleeping while the app is in fo[...][...and more]"
+- ACTION 4: Jade Green touched on a button that has content_desc "Back"
+- ACTION 5: Jade Green touched on a button that has text "Alarm"
+- ACTION 6: Jade Green touched on a button that has content_desc "Sort by"
+- ACTION 7: Jade Green touched on a button that has text "Day and Alarm time"
+- ACTION 8: Jade Green touched on a button that has text "OK"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Settings"
@@ -1173,9 +1245,10 @@
 - ACTION 2: touched on a checked checkbox that has text "Increase volume gradually"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has text "Alarm"
-- ACTION 2: touched on a button that has text "7:00 am, Mon, Tue, Wed, Thu, Fri"
-- ACTION 3: touched on a checkbox that has text "Vibrate"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has text "Alarm"
+- ACTION 2: Jade Green touched on a button that has text "7:00 am, Mon, Tue, Wed, Thu, Fri"
+- ACTION 3: Jade Green touched on a checkbox that has text "Vibrate"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "Bob"
@@ -1219,35 +1292,43 @@
 - ACTION 10: touched on a checkbox that has resource_id "com.simplemobiletools.contacts.pro:id/contact_checkbox"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Search"
-- ACTION 2: filled a focused textfield that has text "Search" with the text "Bob"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Settings"
-- ACTION 3: touched on a checkbox that has text "Show a dialpad button on the main screen"
-- ACTION 4: touched on a checked checkbox that has text "Show a dialpad button on the main screen"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Export contacts to a .vcf file"
-- ACTION 3: filled a textfield that has text "contacts_2024_10_26_08_09_49" with the text "classmate.vcf"
-- ACTION 4: touched on a button that has text "OK"
-- ACTION 5: filled a textfield that has text "classmate.vcf.vcf" with the text "classmate.vcf"
-- ACTION 6: touched on a button that has text "SAVE"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has text "Bob"
-- ACTION 2: touched on a button that has content-desc "Call contact"
-- ACTION 3: touched on a button that has text "ALLOW"
-- ACTION 4: touched on a button that has content-desc "Call contact"
-- ACTION 5: touched on a button that has content-desc "Call contact"
-- ACTION 6: touched on a button that has content-desc "Call contact"
-- ACTION 7: touched on a button that has text "App info"
-- ACTION 8: touched on a button that has content-desc "Call contact"
-- ACTION 9: touched on a button that has content-desc "More options"
-- ACTION 10: touched on a button that has text "Open with"
-- ACTION 11: touched on a button that has text "Contacts, Details"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Search"
+- ACTION 2: Jade Green filled a focused textfield that has text "Search" with the text "Bob"
+- ACTION 3: Jade Green pressed "BACK" button to navigate back
+- ACTION 4: Jade Green scrolled down on a scrollable area that has text "No items found."
+- ACTION 5: Jade Green touched on a button that has text "Contacts"
+- ACTION 6: Jade Green touched on a button that has text "Bob"
+- ACTION 7: Jade Green touched on a button that has content_desc "Delete"
+- ACTION 8: Jade Green touched on a button that has text "Yes"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Settings"
+- ACTION 3: Jade Green scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, GENERAL[...and more]"
+- ACTION 4: Jade Green touched on a checkbox that has text "Show a dialpad button on the main screen"
+- ACTION 5: Jade Green touched on a checked checkbox that has text "Show a dialpad button on the main screen"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Export contacts to a .vcf file"
+- ACTION 3: Jade Green filled a textfield that has text "contacts_2025_02_16_10_46_03" with the text "classmate.vcf"
+- ACTION 4: Jade Green touched on a button that has text "OK"
+- ACTION 5: Jade Green filled a textfield that has text "classmate.vcf.vcf" with the text "classmate.vcf"
+- ACTION 6: Jade Green touched on a button that has text "SAVE"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Search"
+- ACTION 2: Jade Green filled a focused textfield that has text "Search" with the text "Bob"
+- ACTION 3: Jade Green pressed "BACK" button to navigate back
+- ACTION 4: Jade Green filled a focused textfield that has text "Bob" with the text ""
+- ACTION 5: Jade Green scrolled down on a scrollable area that has text "No contacts found"
+- ACTION 6: Jade Green filled a focused textfield that has text "Bob" with the text ""
+- ACTION 7: Jade Green touched on a button that has text "Favorites"
+- ACTION 8: Jade Green touched on a button that has text "Contacts"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "Bob"
@@ -1256,32 +1337,34 @@
 - ACTION 4: touched on a button that has text "SMS"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Settings"
-- ACTION 2: touched on a button that has text "Manage shown contact fields"
-- ACTION 3: touched on a button that has text "OK"
-- ACTION 4: touched on a button that has text "Manage shown contact fields"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has content-desc "More options"
-- ACTION 3: touched on a button that has text "Contacts"
-- ACTION 4: touched on a button that has content-desc "Sort by"
-- ACTION 5: touched on a button that has text "Date created"
-- ACTION 6: touched on a button that has text "Descending"
-- ACTION 7: touched on a button that has text "OK"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Remove from favorites"
-- ACTION 2: touched on a button that has text "Alice"
-- ACTION 3: touched on a button that has content-desc "Add to favorites"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Settings"
+- ACTION 3: Jade Green touched on a button that has text "Manage shown contact fields"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Sort by"
+- ACTION 2: Jade Green touched on a button that has text "Date created"
+- ACTION 3: Jade Green touched on a button that has text "Descending"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Remove from favorites"
+- ACTION 2: Jade Green touched on a button that has text "Alice"
+- ACTION 3: Jade Green touched on a button that has content_desc "Add to favorites"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Add to favorites"
 - ACTION 2: touched on a button that has text "John Smith"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Settings"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Click to return to previous screen"
+- ACTION 2: Jade Green touched on a button that has content_desc "More options"
+- ACTION 3: Jade Green touched on a button that has text "Settings"
+- ACTION 4: Jade Green touched on a button that has text "Font size, Large"
+- ACTION 5: Jade Green touched on a button that has text "Medium"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Dialpad"
@@ -1289,17 +1372,9 @@
 - ACTION 3: touched on a button that has content-desc "Call number"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has text "Alice"
-- ACTION 2: touched on a button that has text "1 (234) 567-890, Mobile"
-- ACTION 3: touched on a button that has text "Alice"
-- ACTION 4: touched on a button that has text "1 (234) 567-890, Mobile"
-- ACTION 5: touched on a button that has text "Alice"
-- ACTION 6: touched on a button that has text "1 (234) 567-890, Mobile"
-- ACTION 7: touched on a button that has text "Call History"
-- ACTION 8: long touched on a button that has text "Alice (3), 03:18 PM"
-- ACTION 9: touched on a button that has content-desc "Delete"
-- ACTION 10: touched on a button that has text "No"
-- ACTION 11: touched on a button that has text "Contacts"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has text "Alice"
+- ACTION 2: Jade Green touched on a button that has text "1 (234) 567-890, Mobile"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "Add phone number"
@@ -1359,18 +1434,20 @@
 - ACTION 10: long touched on a button that has text "1 (234) 567-890, Mobile"</t>
   </si>
   <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Settings"
+</t>
+  </si>
+  <si>
     <t>- ACTION 1: touched on a button that has text "Favorites"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Search"
-- ACTION 2: touched on a button that has text "Internal, 4.8 GB, free[...and more]"
-- ACTION 3: touched on a button that has content-desc "Back"
-- ACTION 4: touched on a button that has text "Internal, 4.8 GB, free[...and more]"
-- ACTION 5: touched on a button that has content-desc "Back"
-- ACTION 6: touched on a button that has text "Files"
-- ACTION 7: long touched on a button that has text "Alarms, 0 items"
-- ACTION 8: touched on a button that has content-desc "Add to favorites"
-- ACTION 9: touched on a button that has text "OK"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green scrolled down on a scrollable area that has text "Internal, 4.8 GB, free[...and more]"
+- ACTION 2: Jade Green touched on a button that has content_desc "Settings"
+- ACTION 3: Jade Green touched on a button that has text "Manage favorites"
+- ACTION 4: Jade Green touched on a button that has content_desc "Add favorites"
+- ACTION 5: Jade Green touched on a button that has text "Alarms_New, 0 items"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "More options"
@@ -1378,9 +1455,10 @@
 - ACTION 3: touched on a checked checkbox that has text "Require pressing Back twice to leave the app"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Settings"
-- ACTION 2: touched on a button that has text "Customize colors"
-- ACTION 3: touched on a button that has text "Theme, Light"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Settings"
+- ACTION 2: Jade Green touched on a button that has text "Customize colors"
+- ACTION 3: Jade Green touched on a button that has text "Theme, Light"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "Storage"</t>
@@ -1399,9 +1477,15 @@
 - ACTION 4: touched on a button that has text "Just once"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has text "Recents"
-- ACTION 2: touched on a textfield that has text "Search"
-- ACTION 3: filled a focused textfield that has text "Search" with the text "video2.mp4"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Back"
+- ACTION 2: Jade Green touched on a button that has text "Recents"
+- ACTION 3: Jade Green scrolled down on a scrollable area that has text "VID_20250222_234440.mp4, 1,008.3 kB, 22.02.2025, 11:44 PM[...and more]"
+- ACTION 4: Jade Green scrolled down on a scrollable area that has text "VID_20250222_231508.mp4, 378.5 kB, 22.02.2025, 11:15 PM[...and more]"
+- ACTION 5: Jade Green scrolled down on a scrollable area that has text "0 B, 17.02.2025, 08:41 PM, diary.txt (2)[...and more]"
+- ACTION 6: Jade Green scrolled down on a scrollable area that has text "VID_20250215_230942.mp4, 354.7 kB, 15.02.2025, 11:09 PM[...and more]"
+- ACTION 7: Jade Green touched on a button that has content_desc "Search"
+- ACTION 8: Jade Green filled a focused textfield that has text "Search" with the text "video2.mp4"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "Recents"
@@ -1412,17 +1496,10 @@
 - ACTION 6: touched on a button that has text "Test1 (1).m4a, 24.1 kB, 19.10.2024, 06:11 PM"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Search"
-- ACTION 2: filled a focused textfield that has text "Search" with the text "screen_2023-06-30_141247.png"
-- ACTION 3: touched on a button that has text "Internal, 4.8 GB, free[...and more]"
-- ACTION 4: touched on a button that has text "Internal, 4.8 GB, free[...and more]"
-- ACTION 5: touched on a button that has text "Internal, 4.8 GB, free[...and more]"
-- ACTION 6: touched on a button that has text "Internal, 4.8 GB, free[...and more]"
-- ACTION 7: touched on a button that has text "Internal, 4.8 GB, free[...and more]"
-- ACTION 8: touched on a button that has text "Internal, 4.8 GB, free[...and more]"
-- ACTION 9: touched on a button that has text "Internal, 4.8 GB, free[...and more]"
-- ACTION 10: touched on a button that has text "Internal, 4.8 GB, free[...and more]"
-- ACTION 11: touched on a button that has text "Internal, 4.8 GB, free[...and more]"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Search"
+- ACTION 2: Jade Green filled a focused textfield that has text "Search" with the text "screen_2023-06-30_141247.png"
+- ACTION 3: Jade Green touched on a button that has text "Internal, 4.8 GB, free[...and more]"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Sort by"
@@ -1436,14 +1513,10 @@
 - ACTION 4: touched on a button that has text "OK"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Change view type"
-- ACTION 3: touched on a button that has text "OK"
-- ACTION 4: touched on a button that has content-desc "More options"
-- ACTION 5: touched on a button that has text "Change view type"
-- ACTION 6: touched on a button that has text "Grid"
-- ACTION 7: touched on a button that has text "List"
-- ACTION 8: touched on a button that has text "OK"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Change view type"
+- ACTION 3: Jade Green touched on a button that has text "List"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "DCIM, 53"
@@ -1465,27 +1538,26 @@
 - ACTION 3: touched on a checkbox that has text "Remember last video playback position"</t>
   </si>
   <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has text "DCIM, 87"
+</t>
+  </si>
+  <si>
     <t>- ACTION 1: touched on a button that has content-desc "Show all folders content"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Switch to folder view"
-- ACTION 2: touched on a button that has content-desc "More options"
-- ACTION 3: touched on a button that has text "Sort by"
-- ACTION 4: touched on a button that has text "Name"
-- ACTION 5: touched on a button that has text "OK"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has text "MyDearAlice, Draft, Hi Alice, this is a test message to see how the MM[...][...and more]"
-- ACTION 2: touched on a button that has content-desc "Dial number"
-- ACTION 3: long touched on a button that has content-desc "More options"
-- ACTION 4: touched on a button that has content-desc "More options"
-- ACTION 5: touched on a button that has text "Conversation details"
-- ACTION 6: long touched on a button that has text "Alice, 1234567890"
-- ACTION 7: touched on a button that has text "1 (234) 567-890, Mobile"
-- ACTION 8: long touched on a button that has text "Alice, 1234567890"
-- ACTION 9: touched on a button that has text "1 (234) 567-890, Mobile"
-- ACTION 10: touched on a button that has text "Close app"
-- ACTION 11: long touched on a button that has text "Alice, 1234567890"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Sort by"
+- ACTION 3: Jade Green touched on a button that has text "Name"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Settings"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has text "team_discussion, Hi Alice, I hope you’re doing well! I wanted to sh[...], 07:49 PM"
+- ACTION 2: Jade Green touched on a button that has content_desc "Dial number"
+</t>
   </si>
   <si>
     <t>- ACTION 1: long touched on a button that has text "Alice, Draft, Hi Alice, this is a test message to see how the MM[...][...and more]"
@@ -1499,11 +1571,9 @@
 - ACTION 9: touched on a button that has text "OK"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a textfield that has text "Search"
-- ACTION 2: filled a focused textfield that has text "Search" with the text "Bob"
-- ACTION 3: long touched on a button that has text "MyDearAlice, Draft, Hi Alice, this is a test message to see how the MM[...][...and more]"
-- ACTION 4: touched on a button that has content-desc "Delete"
-- ACTION 5: touched on a button that has text "Yes"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Search"
+- ACTION 2: Jade Green filled a focused textfield that has text "Search" with the text "Bob"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Settings"
@@ -1524,25 +1594,24 @@
 - ACTION 3: touched on a button that has text "Mark as Unread"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Settings"
-- ACTION 2: touched on a button that has content-desc "Settings"
-- ACTION 3: touched on a button that has text "Show a character counter at writing messages"
-- ACTION 4: touched on a button that has text "Show a character counter at writing messages"
-- ACTION 5: touched on a button that has text "Show a character counter at writing messages"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has text "Start a conversation"
-- ACTION 2: touched on a button that has text "Alice, 1234567890"
-- ACTION 3: filled a focused textfield that has text "Type a messageâ€¦" with the text "Hi Alice, I wanted to share some exciting news with you! I've been working on a new project that combines technology and art, and it's finally coming together. It's been a long journey, but seeing the pieces fall into place is truly rewarding. I'll send you some images soon!"
-- ACTION 4: touched on a button that has content-desc "Attachment"
-- ACTION 5: touched on a button that has text "Choose photo"
-- ACTION 6: touched on a button that has text "Large files"
-- ACTION 7: touched on a button that has content-desc "Show roots"
-- ACTION 8: touched on a button that has text "Images"
-- ACTION 9: touched on a button that has text "DCIM"
-- ACTION 10: touched on a button that has text "DCIM"
-- ACTION 11: Press the back button because you stayed on the pages not belonging to the target app for too long
-- ACTION 12: touched on a button that has text "Choose photo"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Settings"
+- ACTION 2: Jade Green scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, GENERAL[...and more]"
+- ACTION 3: Jade Green touched on a button that has text "Send long messages as MMS"
+- ACTION 4: Jade Green scrolled down on a scrollable area that has text "Send message on pressing Enter, Enable delivery reports, Send long messages as MMS[...and more]"
+- ACTION 5: Jade Green scrolled down on a scrollable area that has text "Enable delivery reports, Send long messages as MMS, Send group messages as MMS[...and more]"
+- ACTION 6: Jade Green pressed "BACK" button to navigate back
+- ACTION 7: Jade Green touched on a button that has content_desc "Settings"
+- ACTION 8: Jade Green touched on a button that has text "Show a character counter at writing messages"
+- ACTION 9: Jade Green scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, GENERAL[...and more]"
+- ACTION 10: Jade Green scrolled down on a scrollable area that has text "Send message on pressing Enter, Enable delivery reports, Send long messages as MMS[...and more]"
+- ACTION 11: Jade Green scrolled down on a scrollable area that has text "Enable delivery reports, Send long messages as MMS, Send group messages as MMS[...and more]"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has text "team_discussion, Hi Alice, I hope you’re doing well! I wanted to sh[...], 07:44 PM"
+- ACTION 2: Jade Green filled a textfield that has text "Type a message…" with the text "Hi Alice, I hope you're doing well! I wanted to share some exciting updates with you. Over the past few weeks, I've been working on a new project that has really taken off. It's been a lot of work, but I'm thrilled with the progress we've made. How have you been? Looking forward to hearing from you!"
+- ACTION 3: Jade Green touched on a button that has text "MMS"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Settings"
@@ -1551,6 +1620,11 @@
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Settings"
 - ACTION 2: touched on a checkbox that has text "Show a character counter at writing messages"</t>
+  </si>
+  <si>
+    <t>- ACTION 1: touched on a button that has content-desc "Settings"
+- ACTION 2: touched on a button that has text "Customize colors"
+- ACTION 3: touched on a button that has text "Theme, Light"</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has text "Alice, Draft, Hi Alice, this is a test message to see how the MM[...][...and more]"
@@ -1578,28 +1652,15 @@
 - ACTION 2: touched on a button that has text "Recordings, 6 Tracks"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has text "test1, &lt;unknown&gt; â€¢ Recordings, 00:01"
-- ACTION 2: touched on a button that has content-desc "Repeat current song"
-- ACTION 3: touched on a button that has text "test1, &lt;unknown&gt; â€¢ Recordings, 00:01"
-- ACTION 4: touched on a button
-- ACTION 5: touched on a button that has text "test1, &lt;unknown&gt; â€¢ Recordings, 00:01"
-- ACTION 6: touched on a button that has content-desc "Stop playback after current song"
-- ACTION 7: touched on a button that has content-desc "Repeat off"
-- ACTION 8: touched on a button that has content-desc "Repeat all"
-- ACTION 9: touched on a button that has content-desc "Play / Pause"
-- ACTION 10: touched on a button that has content-desc "Previous"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has text "Tracks"
-- ACTION 2: touched on a button that has text "test1, &lt;unknown&gt; â€¢ Recordings, 00:01"
-- ACTION 3: touched on a button that has content-desc "Play / Pause"
-- ACTION 4: touched on a button that has content-desc "Disable shuffle"
-- ACTION 5: touched on a button that has text "test1, &lt;unknown&gt; â€¢ Recordings, 00:01"
-- ACTION 6: touched on a button that has content-desc "Enable shuffle"
-- ACTION 7: touched on a button that has content-desc "Disable shuffle"
-- ACTION 8: touched on a button that has content-desc "Enable shuffle"
-- ACTION 9: touched on a button that has content-desc "Previous"
-- ACTION 10: touched on a button that has content-desc "Play / Pause"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has text "test1, &lt;unknown&gt; • Recordings, 00:01"
+- ACTION 2: Jade Green touched on a button that has content_desc "Play / Pause"
+- ACTION 3: Jade Green touched on a button that has content_desc "Repeat current song"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has text "test1, &lt;unknown&gt; • Recordings, 00:01"
+- ACTION 2: Jade Green touched on a button that has content_desc "Play / Pause"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Search"
@@ -1611,41 +1672,46 @@
 - ACTION 3: touched on a button that has text "5 minutes"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Settings"
-- ACTION 3: touched on a checkbox that has text "Gapless playback"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Sort by"
-- ACTION 2: touched on a button that has text "Date added"
-- ACTION 3: touched on a button that has text "Track number"
-- ACTION 4: touched on a button that has text "Duration"
-- ACTION 5: touched on a button that has text "Date added"
-- ACTION 6: touched on a button that has text "Title"
-- ACTION 7: touched on a button that has text "Descending"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Settings"
-- ACTION 3: touched on a button that has resource_id "com.simplemobiletools.notes.pro:id/settings_gravity_holder"
-- ACTION 4: touched on a button that has content-desc "Open note"
-- ACTION 5: touched on a button that has text "Center Alignment Note"
-- ACTION 6: touched on a button that has content-desc "More options"
-- ACTION 7: touched on a button that has content-desc "Open note"
-- ACTION 8: touched on a button that has text "Center Alignment Note"
-- ACTION 9: touched on a button that has content-desc "More options"
-- ACTION 10: touched on a button that has text "Rename note"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Create a new note"
-- ACTION 2: filled a focused textfield that has text "Label" with the text "test"
-- ACTION 3: touched on a button that has text "OK"
-- ACTION 4: filled a focused textfield that has text "test" with the text "test 2"
-- ACTION 5: touched on a button that has text "OK"
-- ACTION 6: touched on a button that has text "Add new checklist items"
-- ACTION 7: filled a focused textfield that has resource_id "com.simplemobiletools.notes.pro:id/title_edit_text" with the text "Item 1"
-- ACTION 8: touched on a button that has resource_id "com.simplemobiletools.notes.pro:id/add_item"
-- ACTION 9: filled a focused textfield that has resource_id "com.simplemobiletools.notes.pro:id/title_edit_text" with the text "Item 2"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Settings"
+- ACTION 3: Jade Green touched on a checkbox that has text "Gapless playback"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Back"
+- ACTION 2: Jade Green touched on a button that has content_desc "Sort by"
+- ACTION 3: Jade Green touched on a button that has text "Date added"
+- ACTION 4: Jade Green touched on a button that has text "Descending"
+- ACTION 5: Jade Green touched on a button that has text "OK"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Settings"
+- ACTION 3: Jade Green touched on a button that has resource_id "com.simplemobiletools.notes.pro:id/settings_gravity_holder"
+- ACTION 4: Jade Green touched on a button that has content_desc "Open note"
+- ACTION 5: Jade Green touched on a button that has text "Center Alignment Note"
+- ACTION 6: Jade Green touched on a button that has content_desc "More options"
+- ACTION 7: Jade Green pressed "BACK" button to navigate back
+- ACTION 8: Jade Green touched on a button that has content_desc "Open note"
+- ACTION 9: Jade Green touched on a button that has text "Center Alignment Note"
+- ACTION 10: Jade Green touched on a button that has content_desc "More options"
+- ACTION 11: Jade Green pressed "BACK" button to navigate back
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Create a new note"
+- ACTION 2: Jade Green filled a focused textfield that has text "Label" with the text "test"
+- ACTION 3: Jade Green touched on a button that has text "OK"
+- ACTION 4: Jade Green filled a focused textfield that has text "test" with the text "test1"
+- ACTION 5: Jade Green touched on a button that has text "OK"
+- ACTION 6: Jade Green filled a focused textfield that has text "test1" with the text "test2"
+- ACTION 7: Jade Green filled a focused textfield that has text "test2" with the text "test_new"
+- ACTION 8: Jade Green touched on a button that has text "OK"
+- ACTION 9: Jade Green touched on a button that has content_desc "More options"
+- ACTION 10: Jade Green pressed "BACK" button to navigate back
+- ACTION 11: Jade Green touched on a button that has text "Add new checklist items"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Create a new note"
@@ -1680,7 +1746,12 @@
 - ACTION 3: touched on a checked checkbox that has text "Autosave notes"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Open note"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Print"
+- ACTION 3: Jade Green touched on a button that has content_desc "Save to PDF"
+- ACTION 4: Jade Green filled a textfield that has text "test_unique_3" with the text "diary.pdf"
+- ACTION 5: Jade Green touched on a button that has text "SAVE"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "More options"
@@ -1689,13 +1760,11 @@
 - ACTION 4: touched on a button that has text "OK"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "More options"
-- ACTION 2: touched on a button that has text "Settings"
-- ACTION 3: scrolled up on a scrollable area that has text "STARTUP, Place cursor to the end of note, Show keyboard on startup[...and more]"
-- ACTION 4: touched on a button that has text "Customize colors"</t>
-  </si>
-  <si>
-    <t>- ACTION 1: touched on a button that has text "Word Count Note"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Settings"
+- ACTION 3: Jade Green touched on a button that has text "Customize colors"
+- ACTION 4: Jade Green touched on a button that has text "Theme, Light"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Settings"
@@ -1705,11 +1774,15 @@
 - ACTION 5: touched on a button that has content-desc "Save"</t>
   </si>
   <si>
-    <t>- ACTION 1: touched on a button that has content-desc "Search"
-- ACTION 2: filled a focused textfield that has text "Search" with the text "test1"
-- ACTION 3: touched on a button that has text "Test1 (2).m4a, 00:01, 26.10.2024, 11:32 PM[...and more]"
-- ACTION 4: filled a focused textfield that has text "test1" with the text "test1.m4a"
-- ACTION 5: filled a focused textfield that has text "test1.m4a" with the text "test1"</t>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has text "WHILE USING THE APP"
+- ACTION 2: Jade Green touched on a button that has content_desc "Search"
+- ACTION 3: Jade Green filled a focused textfield that has text "Search" with the text "test1"
+- ACTION 4: Jade Green touched on a button that has content_desc "Settings"
+- ACTION 5: Jade Green touched on a button that has content_desc "Back"
+- ACTION 6: Jade Green touched on a button that has text "Recycle Bin"
+- ACTION 7: Jade Green touched on a button that has content_desc "Search"
+- ACTION 8: Jade Green filled a focused textfield that has text "Search" with the text "test1"
+</t>
   </si>
   <si>
     <t>- ACTION 1: touched on a button that has content-desc "Settings"
@@ -1733,6 +1806,116 @@
 - ACTION 2: touched on a button that has content-desc "Play / Pause"</t>
   </si>
   <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "New Event"
+- ACTION 2: Jade Green filled a focused textfield that has text "Title" with the text "VisitParents"
+- ACTION 3: Jade Green touched on a button that has text "February 24 (Mon)"
+- ACTION 4: Jade Green scrolled right on a scrollable area that has text "1, 2, 3[...and more]"
+- ACTION 5: Jade Green touched on a button that has text "30"
+- ACTION 6: Jade Green touched on a button that has content_desc "Previous month"
+- ACTION 7: Jade Green touched on a button that has text "30"
+- ACTION 8: Jade Green touched on a button that has content_desc "Next month"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Add holidays"
+- ACTION 3: Jade Green scrolled down on a scrollable area that has text "Algeria, Argentina, Australia[...and more]"
+- ACTION 4: Jade Green scrolled down on a scrollable area that has text "Hellas, Hrvatska, India[...and more]"
+- ACTION 5: Jade Green touched on a button that has text "South Africa"
+- ACTION 6: Jade Green touched on a button that has text "OK"
+- ACTION 7: Jade Green touched on a button that has content_desc "Filter events by type"
+- ACTION 8: Jade Green touched on a button that has text "OK"
+- ACTION 9: Jade Green touched on a button that has content_desc "Search"
+- ACTION 10: Jade Green filled a focused textfield that has text "Search" with the text "2023"
+- ACTION 11: Jade Green touched on a button that has content_desc "Change view"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has text "Groups"
+- ACTION 2: Jade Green touched on a button that has content_desc "Create group"
+- ACTION 3: Jade Green filled a focused textfield that has text "Title" with the text "Classmates"
+- ACTION 4: Jade Green touched on a button that has text "OK"
+- ACTION 5: Jade Green touched on a button that has text "Classmates (0)"
+- ACTION 6: Jade Green touched on a button that has text "Add contacts"
+- ACTION 7: Jade Green touched on a checkbox that has resource_id "com.simplemobiletools.contacts.pro:id/contact_checkbox"
+- ACTION 8: Jade Green touched on a checked checkbox that has resource_id "com.simplemobiletools.contacts.pro:id/contact_checkbox"
+- ACTION 9: Jade Green touched on a checkbox that has resource_id "com.simplemobiletools.contacts.pro:id/contact_checkbox"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Dialpad"
+- ACTION 3: Jade Green filled a focused textfield that has resource_id "com.simplemobiletools.dialer:id/dialpad_input" with the text "911"
+- ACTION 4: Jade Green touched on a button that has content_desc "Call number"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has text "Call History"
+- ACTION 2: Jade Green touched on a button that has content_desc "Search"
+- ACTION 3: Jade Green filled a focused textfield that has text "Search" with the text "Bob"
+- ACTION 4: Jade Green touched on a button that has content_desc "Filter"
+- ACTION 5: Jade Green touched on a button that has text "OK"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Settings"
+- ACTION 3: Jade Green touched on a button that has text "Customize colors"
+- ACTION 4: Jade Green touched on a button that has text "Theme, Dark"
+- ACTION 5: Jade Green touched on a button that has text "OK"
+- ACTION 6: Jade Green touched on a button that has text "Light"
+- ACTION 7: Jade Green touched on a button that has content_desc "Save"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has resource_id "com.simplemobiletools.filemanager.pro:id/expand_button"
+- ACTION 2: Jade Green touched on a button that has text "SD Card, 835.5 MB, free[...and more]"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Settings"
+- ACTION 2: Jade Green touched on a checked checkbox that has text "Show hidden items"
+- ACTION 3: Jade Green touched on a checkbox that has text "Show hidden items"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Settings"
+- ACTION 3: Jade Green scrolled down on a scrollable area that has text "COLOR CUSTOMIZATION, Customize colors, GENERAL[...and more]"
+- ACTION 4: Jade Green scrolled down on a scrollable area that has text "Allow controlling video volume and brightness with[...], THUMBNAILS, Crop thumbnails into squares[...and more]"
+- ACTION 5: Jade Green scrolled down on a scrollable area that has text "Allow controlling photo brightness with vertical g[...], Allow closing the fullscreen view with a down gest[...], Show a notch if available[...and more]"
+- ACTION 6: Jade Green scrolled down on a scrollable area that has text "Password protect file deletion and moving, FILE OPERATIONS, Delete empty folders after deleting their content[...and more]"
+- ACTION 7: Jade Green scrolled down on a scrollable area that has text "RECYCLE BIN, Move items into the Recycle Bin instead of deletin[...], Show the Recycle Bin at the folders screen[...and more]"
+- ACTION 8: Jade Green pressed "BACK" button to navigate back
+- ACTION 9: Jade Green touched on a button that has content_desc "More options"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Click to return to previous screen"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "Create a new note"
+- ACTION 2: Jade Green filled a focused textfield that has text "Label" with the text "test"
+- ACTION 3: Jade Green touched on a button that has text "Text note"
+- ACTION 4: Jade Green filled a focused textfield that has text "test" with the text "12345678"
+- ACTION 5: Jade Green touched on a button that has text "OK"
+- ACTION 6: Jade Green pressed "BACK" button to navigate back
+- ACTION 7: Jade Green filled a focused textfield that has text "12345678" with the text "test1"
+- ACTION 8: Jade Green touched on a button that has text "OK"
+- ACTION 9: Jade Green filled a focused textfield that has text "test1" with the text "test_unique"
+- ACTION 10: Jade Green pressed "BACK" button to navigate back
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- ACTION 1: Jade Green touched on a button that has content_desc "More options"
+- ACTION 2: Jade Green touched on a button that has text "Export as file"
+- ACTION 3: Jade Green filled a textfield that has text "test_unique_3.txt" with the text "diary.txt"
+- ACTION 4: Jade Green touched on a button that has text "SAVE"
+- ACTION 5: Jade Green touched on a button that has text "Only export the current file content
+</t>
+  </si>
+  <si>
     <t>['1. Open the Calendar app and navigate to the Main page.', '2. Tap the "More options" button.', '3. Select "Add contact birthdays" from the menu.', '4. Confirm the action by tapping "OK" on the event reminder setup screen.']</t>
   </si>
   <si>
@@ -2549,16 +2732,118 @@
     <t>['To play an audio file, locate and tap on the file name in the list on the Main page.', 'Use the "Play / Pause" button to control playback of the selected audio file.']</t>
   </si>
   <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>voicerecorder</t>
-  </si>
-  <si>
-    <t>messenger</t>
-  </si>
-  <si>
-    <t>contacts</t>
+    <t>The task was not completed successfully as Jade Green did not set the event 'VisitParents' on July 30 with a reminder 1 hour before, and the task was abandoned due to excessive steps and difficulty in selecting the correct date.</t>
+  </si>
+  <si>
+    <t>The task to add South Africa's holidays to the calendar was successful, but listing all events for 2023 was not completed as the search returned "No items found."</t>
+  </si>
+  <si>
+    <t>Jade Green successfully created a new group named "Classmates" and added Alice, Bob, and John Smith to the group. However, the task to text the group "GatheringInTheOldPlace" was not completed.</t>
+  </si>
+  <si>
+    <t>Jade Green attempted to call 911 using the dialpad, but after initiating the call, the app returned to the Main page without confirming whether the call was successfully placed or not.</t>
+  </si>
+  <si>
+    <t>The task was not successful as no previous calls with "Bob" were found in the call history.</t>
+  </si>
+  <si>
+    <t>Jade Green successfully switched the custom colors to light and saved the changes, navigating back to the Settings page.</t>
+  </si>
+  <si>
+    <t>Jade Green successfully navigated to the storage settings screen, revealing details about internal and SD card storage.</t>
+  </si>
+  <si>
+    <t>Jade Green successfully enabled the display of hidden files by checking the "Show hidden items" checkbox in the Settings page.</t>
+  </si>
+  <si>
+    <t>Jade Green attempted to disable the display of GIF images but did not complete the task successfully due to a lack of clear steps or settings to achieve this specific goal.</t>
+  </si>
+  <si>
+    <t>Jade Green attempted to change the name of the chat with Alice to 'team_discussion', but the task was not completed successfully due to an incorrect action that closed the app.</t>
+  </si>
+  <si>
+    <t>Jade Green successfully switched the custom colors to light on the Customization page.</t>
+  </si>
+  <si>
+    <t>Jade Green attempted to create a text note called "test" with the content "12345678" and search for "234" but encountered issues with duplicate note titles and did not complete the search.</t>
+  </si>
+  <si>
+    <t>Jade Green successfully exported the note 'Diary' as a file named diary.txt, choosing to only export the current file content.</t>
+  </si>
+  <si>
+    <t>['1. Start on the Main page and touch the "New Event" button to open the event creation screen.', '2. Enter "VisitParents" in the Title textfield.', '3. Touch the date button to open the date picker and navigate to July 2025 using the "Next month" button.', '4. Select the 30th of July.', '5. Set a reminder for 1 hour before the event.', '6. Save the event.']</t>
+  </si>
+  <si>
+    <t>['1. Start on the Main page and touch the "More options" button.', '2. Select "Add holidays" and scroll to find and select "South Africa."', '3. Confirm the selection by touching "OK" on the reminder setup screen.', '4. Use the "Search" button to enter "2023" and list events; if no results, ensure holidays are imported and visible.']</t>
+  </si>
+  <si>
+    <t>['1. Navigate to the "Groups" section from the Main page.', '2. Select "Create group" and enter the title "Classmates."', '3. Confirm the creation by selecting "OK."', '4. Access the new "Classmates" group from the list.', '5. Choose "Add contacts" and select Alice, Bob, and Jack by checking their respective checkboxes, then confirm with "OK."', '6. Send a text to the group with the message "GatheringInTheOldPlace."']</t>
+  </si>
+  <si>
+    <t>['1. From the Main page, touch the button with content description "More options."', '2. Select the "Dialpad" option to open the dialpad interface.', '3. Input "911" into the textfield with resource_id "com.simplemobiletools.dialer:id/dialpad_input."', '4. Touch the button with content description "Call number" to initiate the call.', '5. Ensure the call is successfully placed before exiting the dialpad.']</t>
+  </si>
+  <si>
+    <t>['1. From the Main page, touch the "Call History" button.', '2. Touch the "Search" button to activate the search input field.', '3. Enter "Bob" in the search input field to search for calls with Bob.']</t>
+  </si>
+  <si>
+    <t>['1. Touch the "More options" button on the Main screen.', '2. Select "Settings" from the options.', '3. In the Settings screen, touch "Customize colors."', '4. On the Customization screen, touch the "Theme, Dark" button to reveal theme options.', '5. Acknowledge the warning by touching the "OK" button.', '6. Choose the "Light" theme option.', '7. Save the changes by touching the "Save" button.']</t>
+  </si>
+  <si>
+    <t>['1. Touch the button that expands the storage options on the main page.', '2. Select the button labeled "SD Card" to view detailed information about the SD card storage.']</t>
+  </si>
+  <si>
+    <t>['1. Navigate to the Settings page by selecting the button with content_desc "Settings" on the Main page.', '2. Touch the checkbox with the text "Show hidden items" to enable the display of hidden files.']</t>
+  </si>
+  <si>
+    <t>['1. Start from the Main page and touch on the "More options" button.', '2. Select "Filter media" from the expanded menu to access media filtering options.', '3. Look for an option to exclude GIF images from being displayed if available.']</t>
+  </si>
+  <si>
+    <t>['1. From the Main page, locate the textview with text "team_discussion" which represents the chat with Alice.', '2. Tap on the textview to enter the ConversationDetails page.', "3. Use the option within the ConversationDetails page to rename the chat to 'team_discussion'."]</t>
+  </si>
+  <si>
+    <t>['1. Start by tapping the "Create a new note" button.', '2. Enter a unique title for the note, like "test_unique," to avoid duplicate title errors.', '3. Select "Text note" to create a text-based note.', '4. Enter the desired content, such as "12345678," in the note\'s textfield.', '5. Tap "OK" to save the note.', '6. Ensure the note is saved successfully without duplicate title errors.', '7. Use the search feature in the Main page to look for "234" within the notes.']</t>
+  </si>
+  <si>
+    <t>['1. Open the Main page and touch the "More options" button.', '2. Select "Export as file" from the menu.', '3. In the file picker screen, change the filename to "diary.txt".', '4. Touch the "SAVE" button.', '5. Select "Only export the current file content" to complete the export process.']</t>
+  </si>
+  <si>
+    <t>['Ensure the correct month and year are selected before choosing the date to avoid unnecessary navigation.', 'Confirm the reminder setting before saving the event to ensure it is set as intended.']</t>
+  </si>
+  <si>
+    <t>['Ensure that holidays are fully imported and visible before attempting to list events for a specific year.']</t>
+  </si>
+  <si>
+    <t>['Ensure all intended contacts (Alice, Bob, and Jack) are selected before confirming the addition to the group.', 'After adding contacts to the group, proceed to send the intended message to complete the task.']</t>
+  </si>
+  <si>
+    <t>['Before exiting the dialpad, confirm that the call connection was successful to ensure the task is completed.', 'Avoid actions that lead to unintended exits from the dialpad to maintain focus on the task.']</t>
+  </si>
+  <si>
+    <t>['Ensure the name "Bob" is correctly entered in the search field to find relevant call history.', 'If no results are found, verify that the contact exists and has a call history.']</t>
+  </si>
+  <si>
+    <t>['To switch custom colors to light, navigate through Main &gt; Settings &gt; Customize colors.', 'Always confirm theme changes by saving them on the Customization screen.']</t>
+  </si>
+  <si>
+    <t>['To change the storage type to SD card, first expand the storage options on the main page.', 'Select the "SD Card" option to access detailed SD card storage settings.']</t>
+  </si>
+  <si>
+    <t>['To temporarily show hidden files, navigate to the Settings page and check the "Show hidden items" checkbox.']</t>
+  </si>
+  <si>
+    <t>['When attempting to filter media types, access the "Filter media" option from the "More options" menu.', 'Ensure to identify and utilize specific settings or options related to excluding GIFs if they exist within the app.']</t>
+  </si>
+  <si>
+    <t>['Ensure that when trying to rename a chat, do not press buttons that might lead to closing the app.', 'Always confirm you are in the correct page (ConversationDetails) before attempting to rename a chat.']</t>
+  </si>
+  <si>
+    <t>['To switch custom colors to light, navigate to "Settings" and select "Customize colors."', 'On the "Customization" page, ensure the "Light" theme option is selected to switch to light.']</t>
+  </si>
+  <si>
+    <t>['Always ensure the note title is unique to avoid errors when saving.', 'Use the search function on the Main page to find specific text within existing notes.']</t>
+  </si>
+  <si>
+    <t>['Always verify the filename before saving to ensure it matches the desired export name.', 'Choose the option to only export the current file content if you do not wish to update the note itself.']</t>
   </si>
 </sst>
 </file>
@@ -2926,12 +3211,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="31.1796875" customWidth="1"/>
-    <col min="2" max="2" width="47.6328125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -2964,51 +3245,51 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="D2" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="G2" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="H2" t="s">
-        <v>550</v>
+        <v>584</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D3" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E3">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="G3" t="s">
-        <v>415</v>
+        <v>449</v>
       </c>
       <c r="H3" t="s">
-        <v>551</v>
+        <v>585</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -3016,25 +3297,25 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="D4" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E4">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="G4" t="s">
-        <v>416</v>
+        <v>450</v>
       </c>
       <c r="H4" t="s">
-        <v>552</v>
+        <v>586</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -3042,25 +3323,25 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="D5" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="G5" t="s">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="H5" t="s">
-        <v>553</v>
+        <v>587</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -3068,25 +3349,25 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E6">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="G6" t="s">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="H6" t="s">
-        <v>554</v>
+        <v>588</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -3094,51 +3375,51 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D7" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E7">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="G7" t="s">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="H7" t="s">
-        <v>555</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D8" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="G8" t="s">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="H8" t="s">
-        <v>556</v>
+        <v>590</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -3146,51 +3427,51 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="D9" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E9">
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="G9" t="s">
-        <v>421</v>
+        <v>455</v>
       </c>
       <c r="H9" t="s">
-        <v>557</v>
+        <v>591</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D10" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="G10" t="s">
-        <v>422</v>
+        <v>456</v>
       </c>
       <c r="H10" t="s">
-        <v>558</v>
+        <v>592</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -3198,103 +3479,103 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D11" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="G11" t="s">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="H11" t="s">
-        <v>559</v>
+        <v>593</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D12" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E12">
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="G12" t="s">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="H12" t="s">
-        <v>560</v>
+        <v>594</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D13" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="E13">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="G13" t="s">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="H13" t="s">
-        <v>561</v>
+        <v>595</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="D14" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E14">
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="G14" t="s">
-        <v>426</v>
+        <v>460</v>
       </c>
       <c r="H14" t="s">
-        <v>562</v>
+        <v>596</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -3302,51 +3583,51 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="D15" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="G15" t="s">
-        <v>427</v>
+        <v>461</v>
       </c>
       <c r="H15" t="s">
-        <v>563</v>
+        <v>597</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="D16" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E16">
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="G16" t="s">
-        <v>428</v>
+        <v>462</v>
       </c>
       <c r="H16" t="s">
-        <v>564</v>
+        <v>598</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -3354,25 +3635,25 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="G17" t="s">
-        <v>429</v>
+        <v>463</v>
       </c>
       <c r="H17" t="s">
-        <v>565</v>
+        <v>599</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -3380,3119 +3661,3457 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="D18" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E18">
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="G18" t="s">
-        <v>430</v>
+        <v>464</v>
       </c>
       <c r="H18" t="s">
-        <v>566</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="D19" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="G19" t="s">
-        <v>431</v>
+        <v>465</v>
       </c>
       <c r="H19" t="s">
-        <v>567</v>
+        <v>601</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="D20" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F20" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="G20" t="s">
-        <v>432</v>
+        <v>466</v>
       </c>
       <c r="H20" t="s">
-        <v>568</v>
+        <v>602</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="G21" t="s">
-        <v>433</v>
+        <v>467</v>
       </c>
       <c r="H21" t="s">
-        <v>569</v>
+        <v>603</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F22" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="G22" t="s">
-        <v>434</v>
+        <v>468</v>
       </c>
       <c r="H22" t="s">
-        <v>570</v>
+        <v>604</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E23">
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="G23" t="s">
-        <v>435</v>
+        <v>469</v>
       </c>
       <c r="H23" t="s">
-        <v>571</v>
+        <v>605</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="G24" t="s">
-        <v>436</v>
+        <v>470</v>
       </c>
       <c r="H24" t="s">
-        <v>572</v>
+        <v>606</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="D25" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="E25">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="G25" t="s">
-        <v>437</v>
+        <v>471</v>
       </c>
       <c r="H25" t="s">
-        <v>573</v>
+        <v>607</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="D26" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E26">
         <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="G26" t="s">
-        <v>438</v>
+        <v>472</v>
       </c>
       <c r="H26" t="s">
-        <v>574</v>
+        <v>608</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="D27" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E27">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="G27" t="s">
-        <v>439</v>
+        <v>473</v>
       </c>
       <c r="H27" t="s">
-        <v>575</v>
+        <v>609</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="D28" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E28">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="G28" t="s">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="H28" t="s">
-        <v>576</v>
+        <v>610</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="D29" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="G29" t="s">
-        <v>441</v>
+        <v>475</v>
       </c>
       <c r="H29" t="s">
-        <v>577</v>
+        <v>611</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="D30" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="G30" t="s">
-        <v>442</v>
+        <v>476</v>
       </c>
       <c r="H30" t="s">
-        <v>578</v>
+        <v>612</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="D31" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E31">
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="G31" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="H31" t="s">
-        <v>579</v>
+        <v>613</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="D32" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="E32">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="G32" t="s">
-        <v>444</v>
+        <v>478</v>
       </c>
       <c r="H32" t="s">
-        <v>580</v>
+        <v>614</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="D33" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="G33" t="s">
-        <v>445</v>
+        <v>479</v>
       </c>
       <c r="H33" t="s">
-        <v>581</v>
+        <v>615</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="D34" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="G34" t="s">
-        <v>446</v>
+        <v>480</v>
       </c>
       <c r="H34" t="s">
-        <v>582</v>
+        <v>616</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="D35" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="G35" t="s">
-        <v>447</v>
+        <v>481</v>
       </c>
       <c r="H35" t="s">
-        <v>583</v>
+        <v>617</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="D36" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E36">
         <v>5</v>
       </c>
       <c r="F36" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="G36" t="s">
-        <v>448</v>
+        <v>482</v>
       </c>
       <c r="H36" t="s">
-        <v>584</v>
+        <v>618</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="D37" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="G37" t="s">
-        <v>449</v>
+        <v>483</v>
       </c>
       <c r="H37" t="s">
-        <v>585</v>
+        <v>619</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D38" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E38">
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="G38" t="s">
-        <v>450</v>
+        <v>484</v>
       </c>
       <c r="H38" t="s">
-        <v>586</v>
+        <v>620</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="D39" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E39">
         <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="G39" t="s">
-        <v>451</v>
+        <v>485</v>
       </c>
       <c r="H39" t="s">
-        <v>587</v>
+        <v>621</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="D40" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E40">
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="G40" t="s">
-        <v>452</v>
+        <v>486</v>
       </c>
       <c r="H40" t="s">
-        <v>588</v>
+        <v>622</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="D41" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="G41" t="s">
-        <v>453</v>
+        <v>487</v>
       </c>
       <c r="H41" t="s">
-        <v>589</v>
+        <v>623</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="D42" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E42">
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="G42" t="s">
-        <v>454</v>
+        <v>488</v>
       </c>
       <c r="H42" t="s">
-        <v>590</v>
+        <v>624</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="D43" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E43">
         <v>2</v>
       </c>
       <c r="F43" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="G43" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="H43" t="s">
-        <v>591</v>
+        <v>625</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="D44" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E44">
         <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="G44" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="H44" t="s">
-        <v>592</v>
+        <v>626</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C45" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="D45" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E45">
         <v>3</v>
       </c>
       <c r="F45" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="G45" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="H45" t="s">
-        <v>593</v>
+        <v>627</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>689</v>
+        <v>13</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="D46" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E46">
         <v>2</v>
       </c>
       <c r="F46" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="G46" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
       <c r="H46" t="s">
-        <v>594</v>
+        <v>628</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>689</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C47" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="D47" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E47">
         <v>4</v>
       </c>
       <c r="F47" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="G47" t="s">
-        <v>459</v>
+        <v>493</v>
       </c>
       <c r="H47" t="s">
-        <v>595</v>
+        <v>629</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>689</v>
+        <v>13</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C48" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="D48" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E48">
         <v>3</v>
       </c>
       <c r="F48" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="G48" t="s">
-        <v>460</v>
+        <v>494</v>
       </c>
       <c r="H48" t="s">
-        <v>596</v>
+        <v>630</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>689</v>
+        <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="D49" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E49">
         <v>5</v>
       </c>
       <c r="F49" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="G49" t="s">
-        <v>461</v>
+        <v>495</v>
       </c>
       <c r="H49" t="s">
-        <v>597</v>
+        <v>631</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>689</v>
+        <v>13</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C50" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="D50" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E50">
         <v>5</v>
       </c>
       <c r="F50" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="G50" t="s">
-        <v>462</v>
+        <v>496</v>
       </c>
       <c r="H50" t="s">
-        <v>598</v>
+        <v>632</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>689</v>
+        <v>13</v>
       </c>
       <c r="B51" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C51" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="D51" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E51">
         <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="G51" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H51" t="s">
-        <v>599</v>
+        <v>633</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>689</v>
+        <v>13</v>
       </c>
       <c r="B52" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C52" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="D52" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="G52" t="s">
-        <v>464</v>
+        <v>498</v>
       </c>
       <c r="H52" t="s">
-        <v>600</v>
+        <v>634</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>689</v>
+        <v>13</v>
       </c>
       <c r="B53" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C53" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D53" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E53">
         <v>5</v>
       </c>
       <c r="F53" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="G53" t="s">
-        <v>465</v>
+        <v>499</v>
       </c>
       <c r="H53" t="s">
-        <v>601</v>
+        <v>635</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>689</v>
+        <v>13</v>
       </c>
       <c r="B54" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="D54" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E54">
         <v>6</v>
       </c>
       <c r="F54" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="G54" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="H54" t="s">
-        <v>602</v>
+        <v>636</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>689</v>
+        <v>13</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C55" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="D55" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E55">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F55" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="G55" t="s">
-        <v>467</v>
+        <v>501</v>
       </c>
       <c r="H55" t="s">
-        <v>603</v>
+        <v>637</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>689</v>
+        <v>13</v>
       </c>
       <c r="B56" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="D56" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E56">
         <v>4</v>
       </c>
       <c r="F56" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="G56" t="s">
-        <v>468</v>
+        <v>502</v>
       </c>
       <c r="H56" t="s">
-        <v>604</v>
+        <v>638</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>689</v>
+        <v>13</v>
       </c>
       <c r="B57" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C57" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="D57" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F57" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="G57" t="s">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="H57" t="s">
-        <v>605</v>
+        <v>639</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>689</v>
+        <v>13</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C58" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="D58" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E58">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F58" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="G58" t="s">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="H58" t="s">
-        <v>606</v>
+        <v>640</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="D59" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E59">
         <v>4</v>
       </c>
       <c r="F59" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="G59" t="s">
-        <v>471</v>
+        <v>505</v>
       </c>
       <c r="H59" t="s">
-        <v>607</v>
+        <v>641</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="D60" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E60">
         <v>3</v>
       </c>
       <c r="F60" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="G60" t="s">
-        <v>472</v>
+        <v>506</v>
       </c>
       <c r="H60" t="s">
-        <v>608</v>
+        <v>642</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C61" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="D61" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F61" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="G61" t="s">
-        <v>473</v>
+        <v>507</v>
       </c>
       <c r="H61" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B62" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C62" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="D62" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E62">
         <v>4</v>
       </c>
       <c r="F62" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="G62" t="s">
-        <v>474</v>
+        <v>508</v>
       </c>
       <c r="H62" t="s">
-        <v>610</v>
+        <v>644</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C63" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="D63" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="E63">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F63" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="G63" t="s">
-        <v>475</v>
+        <v>509</v>
       </c>
       <c r="H63" t="s">
-        <v>611</v>
+        <v>645</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C64" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="D64" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E64">
         <v>7</v>
       </c>
       <c r="F64" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="G64" t="s">
-        <v>476</v>
+        <v>510</v>
       </c>
       <c r="H64" t="s">
-        <v>612</v>
+        <v>646</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C65" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D65" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E65">
         <v>5</v>
       </c>
       <c r="F65" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="G65" t="s">
-        <v>477</v>
+        <v>511</v>
       </c>
       <c r="H65" t="s">
-        <v>613</v>
+        <v>647</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C66" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="D66" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E66">
         <v>3</v>
       </c>
       <c r="F66" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="G66" t="s">
-        <v>478</v>
+        <v>512</v>
       </c>
       <c r="H66" t="s">
-        <v>614</v>
+        <v>648</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="D67" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E67">
         <v>3</v>
       </c>
       <c r="F67" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="G67" t="s">
-        <v>479</v>
+        <v>513</v>
       </c>
       <c r="H67" t="s">
-        <v>615</v>
+        <v>649</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C68" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="D68" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E68">
         <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="G68" t="s">
-        <v>480</v>
+        <v>514</v>
       </c>
       <c r="H68" t="s">
-        <v>616</v>
+        <v>650</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C69" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="D69" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E69">
         <v>7</v>
       </c>
       <c r="F69" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="G69" t="s">
-        <v>481</v>
+        <v>515</v>
       </c>
       <c r="H69" t="s">
-        <v>617</v>
+        <v>651</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C70" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="D70" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E70">
         <v>2</v>
       </c>
       <c r="F70" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="G70" t="s">
-        <v>482</v>
+        <v>516</v>
       </c>
       <c r="H70" t="s">
-        <v>618</v>
+        <v>652</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C71" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="D71" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E71">
         <v>3</v>
       </c>
       <c r="F71" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="G71" t="s">
-        <v>483</v>
+        <v>517</v>
       </c>
       <c r="H71" t="s">
-        <v>619</v>
+        <v>653</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C72" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="D72" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E72">
         <v>14</v>
       </c>
       <c r="F72" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="G72" t="s">
-        <v>484</v>
+        <v>518</v>
       </c>
       <c r="H72" t="s">
-        <v>620</v>
+        <v>654</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C73" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="D73" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E73">
         <v>2</v>
       </c>
       <c r="F73" t="s">
-        <v>343</v>
+        <v>374</v>
       </c>
       <c r="G73" t="s">
-        <v>485</v>
+        <v>519</v>
       </c>
       <c r="H73" t="s">
-        <v>621</v>
+        <v>655</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C74" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="D74" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E74">
         <v>1</v>
       </c>
       <c r="F74" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="G74" t="s">
-        <v>486</v>
+        <v>520</v>
       </c>
       <c r="H74" t="s">
-        <v>622</v>
+        <v>656</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B75" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C75" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="D75" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="E75">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F75" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="G75" t="s">
-        <v>487</v>
+        <v>521</v>
       </c>
       <c r="H75" t="s">
-        <v>623</v>
+        <v>657</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B76" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C76" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="D76" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E76">
         <v>4</v>
       </c>
       <c r="F76" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="G76" t="s">
-        <v>488</v>
+        <v>522</v>
       </c>
       <c r="H76" t="s">
-        <v>624</v>
+        <v>658</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B77" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C77" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="D77" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E77">
         <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="G77" t="s">
-        <v>489</v>
+        <v>523</v>
       </c>
       <c r="H77" t="s">
-        <v>625</v>
+        <v>659</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B78" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C78" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="D78" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E78">
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="G78" t="s">
-        <v>490</v>
+        <v>524</v>
       </c>
       <c r="H78" t="s">
-        <v>626</v>
+        <v>660</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B79" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C79" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="D79" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E79">
         <v>5</v>
       </c>
       <c r="F79" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="G79" t="s">
-        <v>491</v>
+        <v>525</v>
       </c>
       <c r="H79" t="s">
-        <v>627</v>
+        <v>661</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C80" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="D80" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E80">
         <v>6</v>
       </c>
       <c r="F80" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="G80" t="s">
-        <v>492</v>
+        <v>526</v>
       </c>
       <c r="H80" t="s">
-        <v>628</v>
+        <v>662</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B81" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C81" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="D81" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E81">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F81" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="G81" t="s">
-        <v>493</v>
+        <v>527</v>
       </c>
       <c r="H81" t="s">
-        <v>629</v>
+        <v>663</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B82" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C82" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="D82" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E82">
         <v>10</v>
       </c>
       <c r="F82" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="G82" t="s">
-        <v>494</v>
+        <v>528</v>
       </c>
       <c r="H82" t="s">
-        <v>630</v>
+        <v>664</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B83" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C83" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="D83" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E83">
         <v>11</v>
       </c>
       <c r="F83" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="G83" t="s">
-        <v>495</v>
+        <v>529</v>
       </c>
       <c r="H83" t="s">
-        <v>631</v>
+        <v>665</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B84" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C84" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D84" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E84">
         <v>3</v>
       </c>
       <c r="F84" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="G84" t="s">
-        <v>496</v>
+        <v>530</v>
       </c>
       <c r="H84" t="s">
-        <v>632</v>
+        <v>666</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C85" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="D85" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E85">
         <v>4</v>
       </c>
       <c r="F85" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="G85" t="s">
-        <v>497</v>
+        <v>531</v>
       </c>
       <c r="H85" t="s">
-        <v>633</v>
+        <v>667</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B86" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C86" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="D86" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E86">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F86" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="G86" t="s">
-        <v>498</v>
+        <v>532</v>
       </c>
       <c r="H86" t="s">
-        <v>634</v>
+        <v>668</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C87" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="D87" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E87">
         <v>5</v>
       </c>
       <c r="F87" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="G87" t="s">
-        <v>499</v>
+        <v>533</v>
       </c>
       <c r="H87" t="s">
-        <v>635</v>
+        <v>669</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B88" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C88" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="D88" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E88">
         <v>2</v>
       </c>
       <c r="F88" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="G88" t="s">
-        <v>500</v>
+        <v>534</v>
       </c>
       <c r="H88" t="s">
-        <v>636</v>
+        <v>670</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B89" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C89" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="D89" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E89">
         <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="G89" t="s">
-        <v>501</v>
+        <v>535</v>
       </c>
       <c r="H89" t="s">
-        <v>637</v>
+        <v>671</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B90" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C90" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="D90" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E90">
         <v>4</v>
       </c>
       <c r="F90" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="G90" t="s">
-        <v>502</v>
+        <v>536</v>
       </c>
       <c r="H90" t="s">
-        <v>638</v>
+        <v>672</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B91" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C91" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="D91" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="G91" t="s">
-        <v>503</v>
+        <v>537</v>
       </c>
       <c r="H91" t="s">
-        <v>639</v>
+        <v>673</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B92" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C92" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="D92" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E92">
         <v>1</v>
       </c>
       <c r="F92" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="G92" t="s">
-        <v>504</v>
+        <v>538</v>
       </c>
       <c r="H92" t="s">
-        <v>640</v>
+        <v>674</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B93" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C93" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="D93" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E93">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F93" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="G93" t="s">
-        <v>505</v>
+        <v>539</v>
       </c>
       <c r="H93" t="s">
-        <v>641</v>
+        <v>675</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="B94" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="D94" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E94">
         <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>313</v>
+        <v>395</v>
       </c>
       <c r="G94" t="s">
-        <v>506</v>
+        <v>540</v>
       </c>
       <c r="H94" t="s">
-        <v>642</v>
+        <v>676</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="B95" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="D95" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E95">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F95" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="G95" t="s">
-        <v>507</v>
+        <v>541</v>
       </c>
       <c r="H95" t="s">
-        <v>643</v>
+        <v>677</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C96" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E96">
         <v>10</v>
       </c>
       <c r="F96" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="G96" t="s">
-        <v>508</v>
+        <v>542</v>
       </c>
       <c r="H96" t="s">
-        <v>644</v>
+        <v>678</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="B97" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C97" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="D97" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="E97">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F97" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="G97" t="s">
-        <v>509</v>
+        <v>543</v>
       </c>
       <c r="H97" t="s">
-        <v>645</v>
+        <v>679</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C98" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="D98" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E98">
         <v>3</v>
       </c>
       <c r="F98" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="G98" t="s">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="H98" t="s">
-        <v>646</v>
+        <v>680</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="B99" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C99" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="D99" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E99">
         <v>5</v>
       </c>
       <c r="F99" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="G99" t="s">
-        <v>511</v>
+        <v>545</v>
       </c>
       <c r="H99" t="s">
-        <v>647</v>
+        <v>681</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C100" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="D100" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E100">
         <v>1</v>
       </c>
       <c r="F100" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="G100" t="s">
-        <v>512</v>
+        <v>546</v>
       </c>
       <c r="H100" t="s">
-        <v>648</v>
+        <v>682</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="B101" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C101" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E101">
         <v>3</v>
       </c>
       <c r="F101" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="G101" t="s">
-        <v>513</v>
+        <v>547</v>
       </c>
       <c r="H101" t="s">
-        <v>649</v>
+        <v>683</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="B102" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C102" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="D102" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E102">
         <v>11</v>
       </c>
       <c r="F102" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="G102" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="H102" t="s">
-        <v>650</v>
+        <v>684</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C103" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="D103" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="E103">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F103" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="G103" t="s">
-        <v>515</v>
+        <v>549</v>
       </c>
       <c r="H103" t="s">
-        <v>651</v>
+        <v>685</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C104" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="D104" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E104">
         <v>3</v>
       </c>
       <c r="F104" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="G104" t="s">
-        <v>516</v>
+        <v>550</v>
       </c>
       <c r="H104" t="s">
-        <v>652</v>
+        <v>686</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C105" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="D105" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E105">
         <v>2</v>
       </c>
       <c r="F105" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="G105" t="s">
-        <v>517</v>
+        <v>551</v>
       </c>
       <c r="H105" t="s">
-        <v>653</v>
+        <v>687</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="B106" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C106" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="D106" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E106">
         <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>358</v>
+        <v>407</v>
       </c>
       <c r="G106" t="s">
-        <v>518</v>
+        <v>552</v>
       </c>
       <c r="H106" t="s">
-        <v>654</v>
+        <v>688</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C107" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="D107" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E107">
         <v>3</v>
       </c>
       <c r="F107" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="G107" t="s">
-        <v>519</v>
+        <v>553</v>
       </c>
       <c r="H107" t="s">
-        <v>655</v>
+        <v>689</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C108" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="D108" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E108">
         <v>1</v>
       </c>
       <c r="F108" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="G108" t="s">
-        <v>520</v>
+        <v>554</v>
       </c>
       <c r="H108" t="s">
-        <v>656</v>
+        <v>690</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B109" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C109" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="D109" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E109">
         <v>2</v>
       </c>
       <c r="F109" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="G109" t="s">
-        <v>521</v>
+        <v>555</v>
       </c>
       <c r="H109" t="s">
-        <v>657</v>
+        <v>691</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B110" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C110" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="D110" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E110">
         <v>7</v>
       </c>
       <c r="F110" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="G110" t="s">
-        <v>522</v>
+        <v>556</v>
       </c>
       <c r="H110" t="s">
-        <v>658</v>
+        <v>692</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B111" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C111" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="D111" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E111">
         <v>2</v>
       </c>
       <c r="F111" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="G111" t="s">
-        <v>523</v>
+        <v>557</v>
       </c>
       <c r="H111" t="s">
-        <v>659</v>
+        <v>693</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B112" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C112" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="D112" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="E112">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F112" t="s">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="G112" t="s">
-        <v>524</v>
+        <v>558</v>
       </c>
       <c r="H112" t="s">
-        <v>660</v>
+        <v>694</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B113" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C113" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="D113" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="E113">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F113" t="s">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="G113" t="s">
-        <v>525</v>
+        <v>559</v>
       </c>
       <c r="H113" t="s">
-        <v>661</v>
+        <v>695</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B114" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="D114" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E114">
         <v>2</v>
       </c>
       <c r="F114" t="s">
-        <v>392</v>
+        <v>415</v>
       </c>
       <c r="G114" t="s">
-        <v>526</v>
+        <v>560</v>
       </c>
       <c r="H114" t="s">
-        <v>662</v>
+        <v>696</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B115" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C115" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="D115" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E115">
         <v>3</v>
       </c>
       <c r="F115" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="G115" t="s">
-        <v>527</v>
+        <v>561</v>
       </c>
       <c r="H115" t="s">
-        <v>663</v>
+        <v>697</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B116" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="D116" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E116">
         <v>3</v>
       </c>
       <c r="F116" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="G116" t="s">
-        <v>528</v>
+        <v>562</v>
       </c>
       <c r="H116" t="s">
-        <v>664</v>
+        <v>698</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B117" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C117" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="D117" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="E117">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F117" t="s">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="G117" t="s">
-        <v>529</v>
+        <v>563</v>
       </c>
       <c r="H117" t="s">
-        <v>665</v>
+        <v>699</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="B118" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C118" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="D118" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E118">
         <v>2</v>
       </c>
       <c r="F118" t="s">
-        <v>343</v>
+        <v>374</v>
       </c>
       <c r="G118" t="s">
-        <v>530</v>
+        <v>564</v>
       </c>
       <c r="H118" t="s">
-        <v>666</v>
+        <v>700</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="B119" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C119" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="D119" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E119">
         <v>12</v>
       </c>
       <c r="F119" t="s">
-        <v>396</v>
+        <v>419</v>
       </c>
       <c r="G119" t="s">
-        <v>531</v>
+        <v>565</v>
       </c>
       <c r="H119" t="s">
-        <v>667</v>
+        <v>701</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="B120" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C120" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="D120" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="E120">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F120" t="s">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="G120" t="s">
-        <v>532</v>
+        <v>566</v>
       </c>
       <c r="H120" t="s">
-        <v>668</v>
+        <v>702</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="B121" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C121" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="D121" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E121">
         <v>5</v>
       </c>
       <c r="F121" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="G121" t="s">
-        <v>533</v>
+        <v>567</v>
       </c>
       <c r="H121" t="s">
-        <v>669</v>
+        <v>703</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="B122" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C122" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="D122" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E122">
         <v>6</v>
       </c>
       <c r="F122" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="G122" t="s">
-        <v>534</v>
+        <v>568</v>
       </c>
       <c r="H122" t="s">
-        <v>670</v>
+        <v>704</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="B123" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C123" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="D123" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E123">
         <v>5</v>
       </c>
       <c r="F123" t="s">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="G123" t="s">
-        <v>535</v>
+        <v>569</v>
       </c>
       <c r="H123" t="s">
-        <v>671</v>
+        <v>705</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="B124" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C124" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="D124" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E124">
         <v>11</v>
       </c>
       <c r="F124" t="s">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="G124" t="s">
-        <v>536</v>
+        <v>570</v>
       </c>
       <c r="H124" t="s">
-        <v>672</v>
+        <v>706</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="B125" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C125" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="D125" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E125">
         <v>4</v>
       </c>
       <c r="F125" t="s">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="G125" t="s">
-        <v>537</v>
+        <v>571</v>
       </c>
       <c r="H125" t="s">
-        <v>673</v>
+        <v>707</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="B126" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C126" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="D126" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="E126">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F126" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G126" t="s">
-        <v>538</v>
+        <v>572</v>
       </c>
       <c r="H126" t="s">
-        <v>674</v>
+        <v>708</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="B127" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C127" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="D127" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E127">
         <v>7</v>
       </c>
       <c r="F127" t="s">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="G127" t="s">
-        <v>539</v>
+        <v>573</v>
       </c>
       <c r="H127" t="s">
-        <v>675</v>
+        <v>709</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="B128" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C128" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="D128" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E128">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F128" t="s">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="G128" t="s">
-        <v>540</v>
+        <v>574</v>
       </c>
       <c r="H128" t="s">
-        <v>676</v>
+        <v>710</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="B129" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C129" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="D129" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="E129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" t="s">
-        <v>406</v>
+        <v>374</v>
       </c>
       <c r="G129" t="s">
-        <v>541</v>
+        <v>575</v>
       </c>
       <c r="H129" t="s">
-        <v>677</v>
+        <v>711</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>687</v>
+        <v>20</v>
       </c>
       <c r="B130" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C130" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="D130" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E130">
         <v>5</v>
       </c>
       <c r="F130" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="G130" t="s">
-        <v>542</v>
+        <v>576</v>
       </c>
       <c r="H130" t="s">
-        <v>678</v>
+        <v>712</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>687</v>
+        <v>20</v>
       </c>
       <c r="B131" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C131" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="D131" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E131">
         <v>2</v>
       </c>
       <c r="F131" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="G131" t="s">
-        <v>543</v>
+        <v>577</v>
       </c>
       <c r="H131" t="s">
-        <v>679</v>
+        <v>713</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>687</v>
+        <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C132" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="D132" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E132">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F132" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="G132" t="s">
-        <v>544</v>
+        <v>578</v>
       </c>
       <c r="H132" t="s">
-        <v>680</v>
+        <v>714</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>687</v>
+        <v>20</v>
       </c>
       <c r="B133" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C133" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="D133" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E133">
         <v>2</v>
       </c>
       <c r="F133" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="G133" t="s">
-        <v>545</v>
+        <v>579</v>
       </c>
       <c r="H133" t="s">
-        <v>681</v>
+        <v>715</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>687</v>
+        <v>20</v>
       </c>
       <c r="B134" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C134" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D134" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E134">
         <v>3</v>
       </c>
       <c r="F134" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="G134" t="s">
-        <v>546</v>
+        <v>580</v>
       </c>
       <c r="H134" t="s">
-        <v>682</v>
+        <v>716</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>687</v>
+        <v>20</v>
       </c>
       <c r="B135" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C135" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="D135" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E135">
         <v>2</v>
       </c>
       <c r="F135" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="G135" t="s">
-        <v>547</v>
+        <v>581</v>
       </c>
       <c r="H135" t="s">
-        <v>683</v>
+        <v>717</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>687</v>
+        <v>20</v>
       </c>
       <c r="B136" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C136" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="D136" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E136">
         <v>2</v>
       </c>
       <c r="F136" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="G136" t="s">
-        <v>548</v>
+        <v>582</v>
       </c>
       <c r="H136" t="s">
-        <v>684</v>
+        <v>718</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>687</v>
+        <v>20</v>
       </c>
       <c r="B137" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C137" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="D137" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E137">
         <v>2</v>
       </c>
       <c r="F137" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="G137" t="s">
-        <v>549</v>
+        <v>583</v>
       </c>
       <c r="H137" t="s">
-        <v>685</v>
+        <v>719</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>9</v>
+      </c>
+      <c r="B138" t="s">
+        <v>153</v>
+      </c>
+      <c r="C138" t="s">
+        <v>720</v>
+      </c>
+      <c r="D138" t="s">
+        <v>301</v>
+      </c>
+      <c r="E138">
+        <v>11</v>
+      </c>
+      <c r="F138" t="s">
+        <v>436</v>
+      </c>
+      <c r="G138" t="s">
+        <v>733</v>
+      </c>
+      <c r="H138" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>9</v>
+      </c>
+      <c r="B139" t="s">
+        <v>154</v>
+      </c>
+      <c r="C139" t="s">
+        <v>721</v>
+      </c>
+      <c r="D139" t="s">
+        <v>301</v>
+      </c>
+      <c r="E139">
+        <v>11</v>
+      </c>
+      <c r="F139" t="s">
+        <v>437</v>
+      </c>
+      <c r="G139" t="s">
+        <v>734</v>
+      </c>
+      <c r="H139" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>13</v>
+      </c>
+      <c r="B140" t="s">
+        <v>155</v>
+      </c>
+      <c r="C140" t="s">
+        <v>722</v>
+      </c>
+      <c r="D140" t="s">
+        <v>301</v>
+      </c>
+      <c r="E140">
+        <v>11</v>
+      </c>
+      <c r="F140" t="s">
+        <v>438</v>
+      </c>
+      <c r="G140" t="s">
+        <v>735</v>
+      </c>
+      <c r="H140" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>13</v>
+      </c>
+      <c r="B141" t="s">
+        <v>156</v>
+      </c>
+      <c r="C141" t="s">
+        <v>723</v>
+      </c>
+      <c r="D141" t="s">
+        <v>301</v>
+      </c>
+      <c r="E141">
+        <v>5</v>
+      </c>
+      <c r="F141" t="s">
+        <v>439</v>
+      </c>
+      <c r="G141" t="s">
+        <v>736</v>
+      </c>
+      <c r="H141" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>14</v>
+      </c>
+      <c r="B142" t="s">
+        <v>157</v>
+      </c>
+      <c r="C142" t="s">
+        <v>724</v>
+      </c>
+      <c r="D142" t="s">
+        <v>301</v>
+      </c>
+      <c r="E142">
+        <v>5</v>
+      </c>
+      <c r="F142" t="s">
+        <v>440</v>
+      </c>
+      <c r="G142" t="s">
+        <v>737</v>
+      </c>
+      <c r="H142" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>14</v>
+      </c>
+      <c r="B143" t="s">
+        <v>158</v>
+      </c>
+      <c r="C143" t="s">
+        <v>725</v>
+      </c>
+      <c r="D143" t="s">
+        <v>302</v>
+      </c>
+      <c r="E143">
+        <v>7</v>
+      </c>
+      <c r="F143" t="s">
+        <v>441</v>
+      </c>
+      <c r="G143" t="s">
+        <v>738</v>
+      </c>
+      <c r="H143" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>159</v>
+      </c>
+      <c r="C144" t="s">
+        <v>726</v>
+      </c>
+      <c r="D144" t="s">
+        <v>302</v>
+      </c>
+      <c r="E144">
+        <v>2</v>
+      </c>
+      <c r="F144" t="s">
+        <v>442</v>
+      </c>
+      <c r="G144" t="s">
+        <v>739</v>
+      </c>
+      <c r="H144" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>160</v>
+      </c>
+      <c r="C145" t="s">
+        <v>727</v>
+      </c>
+      <c r="D145" t="s">
+        <v>302</v>
+      </c>
+      <c r="E145">
+        <v>3</v>
+      </c>
+      <c r="F145" t="s">
+        <v>443</v>
+      </c>
+      <c r="G145" t="s">
+        <v>740</v>
+      </c>
+      <c r="H145" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>16</v>
+      </c>
+      <c r="B146" t="s">
+        <v>161</v>
+      </c>
+      <c r="C146" t="s">
+        <v>728</v>
+      </c>
+      <c r="D146" t="s">
+        <v>301</v>
+      </c>
+      <c r="E146">
+        <v>11</v>
+      </c>
+      <c r="F146" t="s">
+        <v>444</v>
+      </c>
+      <c r="G146" t="s">
+        <v>741</v>
+      </c>
+      <c r="H146" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>17</v>
+      </c>
+      <c r="B147" t="s">
+        <v>162</v>
+      </c>
+      <c r="C147" t="s">
+        <v>729</v>
+      </c>
+      <c r="D147" t="s">
+        <v>301</v>
+      </c>
+      <c r="E147">
+        <v>2</v>
+      </c>
+      <c r="F147" t="s">
+        <v>445</v>
+      </c>
+      <c r="G147" t="s">
+        <v>742</v>
+      </c>
+      <c r="H147" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>17</v>
+      </c>
+      <c r="B148" t="s">
+        <v>158</v>
+      </c>
+      <c r="C148" t="s">
+        <v>730</v>
+      </c>
+      <c r="D148" t="s">
+        <v>302</v>
+      </c>
+      <c r="E148">
+        <v>3</v>
+      </c>
+      <c r="F148" t="s">
+        <v>378</v>
+      </c>
+      <c r="G148" t="s">
+        <v>552</v>
+      </c>
+      <c r="H148" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>19</v>
+      </c>
+      <c r="B149" t="s">
+        <v>163</v>
+      </c>
+      <c r="C149" t="s">
+        <v>731</v>
+      </c>
+      <c r="D149" t="s">
+        <v>301</v>
+      </c>
+      <c r="E149">
+        <v>11</v>
+      </c>
+      <c r="F149" t="s">
+        <v>446</v>
+      </c>
+      <c r="G149" t="s">
+        <v>743</v>
+      </c>
+      <c r="H149" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>19</v>
+      </c>
+      <c r="B150" t="s">
+        <v>164</v>
+      </c>
+      <c r="C150" t="s">
+        <v>732</v>
+      </c>
+      <c r="D150" t="s">
+        <v>302</v>
+      </c>
+      <c r="E150">
+        <v>6</v>
+      </c>
+      <c r="F150" t="s">
+        <v>447</v>
+      </c>
+      <c r="G150" t="s">
+        <v>744</v>
+      </c>
+      <c r="H150" t="s">
+        <v>757</v>
       </c>
     </row>
   </sheetData>
